--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537628</v>
       </c>
       <c r="B2" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122539514</v>
+        <v>122537651</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>91110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477310</v>
+        <v>477295</v>
       </c>
       <c r="R3" t="n">
-        <v>6935416</v>
+        <v>6935382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122537651</v>
+        <v>122569913</v>
       </c>
       <c r="B4" t="n">
-        <v>91097</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477295</v>
+        <v>477310</v>
       </c>
       <c r="R4" t="n">
-        <v>6935382</v>
+        <v>6935416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537628</v>
       </c>
       <c r="B2" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>122537651</v>
       </c>
       <c r="B3" t="n">
-        <v>91110</v>
+        <v>91123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537628</v>
+        <v>122537651</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>91123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477293</v>
+        <v>477295</v>
       </c>
       <c r="R2" t="n">
-        <v>6935409</v>
+        <v>6935382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122537651</v>
+        <v>122537628</v>
       </c>
       <c r="B3" t="n">
-        <v>91123</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477295</v>
+        <v>477293</v>
       </c>
       <c r="R3" t="n">
-        <v>6935382</v>
+        <v>6935409</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537651</v>
       </c>
       <c r="B2" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>122537628</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537651</v>
+        <v>122537628</v>
       </c>
       <c r="B2" t="n">
-        <v>91231</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477295</v>
+        <v>477293</v>
       </c>
       <c r="R2" t="n">
-        <v>6935382</v>
+        <v>6935409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122537628</v>
+        <v>122537651</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>91235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477293</v>
+        <v>477295</v>
       </c>
       <c r="R3" t="n">
-        <v>6935409</v>
+        <v>6935382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
         <v>122569913</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537628</v>
+        <v>122537651</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477293</v>
+        <v>477295</v>
       </c>
       <c r="R2" t="n">
-        <v>6935409</v>
+        <v>6935382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122537651</v>
+        <v>122537628</v>
       </c>
       <c r="B3" t="n">
-        <v>91235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477295</v>
+        <v>477293</v>
       </c>
       <c r="R3" t="n">
-        <v>6935382</v>
+        <v>6935409</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,16 +892,11 @@
         <v>122569913</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 62661-2021 artfynd.xlsx
+++ b/artfynd/A 62661-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>